--- a/Proyecto Interno/food-security-paper/output/tables/table_spe_summary_cona.xlsx
+++ b/Proyecto Interno/food-security-paper/output/tables/table_spe_summary_cona.xlsx
@@ -401,12 +401,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.282 (0.159)</t>
+          <t>0.461 (0.036)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.495 (0.035)</t>
+          <t>0.47 (0.038)</t>
         </is>
       </c>
     </row>
@@ -428,12 +428,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.282 (0.159) [100%]</t>
+          <t>0.461 (0.036) [100%]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.495 (0.035) [100%]</t>
+          <t>0.47 (0.038) [100%]</t>
         </is>
       </c>
     </row>
@@ -455,7 +455,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.002 (0)</t>
+          <t>0.001 (0)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -482,7 +482,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.002 (0) [100%]</t>
+          <t>0.001 (0) [100%]</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -509,12 +509,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.037 (0.005)</t>
+          <t>0.034 (0.005)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.019 (0.003)</t>
+          <t>0.018 (0.003)</t>
         </is>
       </c>
     </row>
@@ -536,12 +536,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.037 (0.005) [100%]</t>
+          <t>0.034 (0.005) [100%]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.019 (0.003) [100%]</t>
+          <t>0.018 (0.003) [100%]</t>
         </is>
       </c>
     </row>
@@ -563,12 +563,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.009 (0.009)</t>
+          <t>0.008 (0.008)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.006 (0.006)</t>
+          <t>0.005 (0.005)</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.016 (0.005) [54.2%]</t>
+          <t>0.014 (0.005) [56.5%]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.011 (0.004) [56.5%]</t>
+          <t>0.01 (0.003) [56.5%]</t>
         </is>
       </c>
     </row>
@@ -617,12 +617,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.002 (0)</t>
+          <t>0.06 (0.019)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.001 (0)</t>
+          <t>0.051 (0.036)</t>
         </is>
       </c>
     </row>
@@ -644,12 +644,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.002 (0) [99.5%]</t>
+          <t>0.06 (0.019) [99.5%]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.001 (0) [87.5%]</t>
+          <t>0.058 (0.032) [87.5%]</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.043 (0.045)</t>
+          <t>0.008 (0.018)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.064 (0.04) [66.7%]</t>
+          <t>0.032 (0.023) [24.5%]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -710,7 +710,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VitaminB12</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -720,12 +720,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.001 (0.01)</t>
+          <t>0.232 (0.195)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.114 (0.088)</t>
+          <t>0 (0)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -737,7 +737,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VitaminB12</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.103 (0.007) [0.9%]</t>
+          <t>0.317 (0.159) [73.1%]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.131 (0.082) [86.6%]</t>
+          <t>— [0%]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -764,7 +764,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Lipids</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.232 (0.195)</t>
+          <t>0.005 (0.01)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -791,7 +791,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Lipids</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.317 (0.159) [73.1%]</t>
+          <t>0.017 (0.011) [30.6%]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -818,7 +818,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Lipids</t>
+          <t>VitaminB12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.005 (0.01)</t>
+          <t>0.001 (0.01)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -845,7 +845,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Lipids</t>
+          <t>VitaminB12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.017 (0.011) [30.6%]</t>
+          <t>0.103 (0.007) [0.9%]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1332,32 +1332,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.483 (0.033)</t>
+          <t>0.491 (0.03)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.19 (0.082)</t>
+          <t>0.436 (0.025)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.172 (0.082)</t>
+          <t>0.456 (0.028)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.522 (0.028)</t>
+          <t>0.492 (0.036)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.47 (0.026)</t>
+          <t>0.444 (0.029)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.493 (0.03)</t>
+          <t>0.473 (0.033)</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.002 (0)</t>
+          <t>0.001 (0)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.002 (0)</t>
+          <t>0.001 (0)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1436,17 +1436,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.039 (0.003)</t>
+          <t>0.037 (0.003)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.037 (0.005)</t>
+          <t>0.035 (0.005)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.034 (0.005)</t>
+          <t>0.032 (0.005)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.018 (0.003)</t>
+          <t>0.017 (0.003)</t>
         </is>
       </c>
     </row>
@@ -1488,22 +1488,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.009 (0.008)</t>
+          <t>0.008 (0.006)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.011 (0.009)</t>
+          <t>0.011 (0.008)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.005 (0.008)</t>
+          <t>0.006 (0.008)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.006 (0.005)</t>
+          <t>0.005 (0.004)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1540,32 +1540,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.002 (0)</t>
+          <t>0.06 (0.016)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.002 (0)</t>
+          <t>0.061 (0.023)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.002 (0)</t>
+          <t>0.058 (0.019)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.001 (0)</t>
+          <t>0.061 (0.038)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.001 (0)</t>
+          <t>0.051 (0.037)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.001 (0)</t>
+          <t>0.04 (0.029)</t>
         </is>
       </c>
     </row>
@@ -1592,17 +1592,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0 (0.001)</t>
+          <t>0 (0)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.075 (0.05)</t>
+          <t>0.01 (0.022)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.053 (0.022)</t>
+          <t>0.014 (0.019)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1624,37 +1624,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>VitaminB12</t>
+          <t>Zinc</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0 (0)</t>
+          <t>0.188 (0.178)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.001 (0.013)</t>
+          <t>0.217 (0.209)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.001 (0.011)</t>
+          <t>0.29 (0.187)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.005 (0.006)</t>
+          <t>0 (0)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.154 (0.051)</t>
+          <t>0 (0)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.182 (0.053)</t>
+          <t>0 (0)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1676,22 +1676,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Zinc</t>
+          <t>Lipids</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0.188 (0.178)</t>
+          <t>0 (0)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.217 (0.209)</t>
+          <t>0 (0)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.29 (0.187)</t>
+          <t>0.016 (0.011)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1728,7 +1728,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lipids</t>
+          <t>VitaminB12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1738,12 +1738,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0 (0)</t>
+          <t>0.001 (0.013)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.016 (0.011)</t>
+          <t>0.001 (0.011)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
